--- a/templates/gs/invoice.xlsx
+++ b/templates/gs/invoice.xlsx
@@ -4,11 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6550"/>
+    <workbookView windowWidth="29400" windowHeight="14100"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="INV" sheetId="2" r:id="rId1"/>
+    <sheet name="PL " sheetId="3" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PL '!$A$17:$M$19</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="60">
   <si>
     <t>GLOBALSINO PTE.LTD.</t>
   </si>
@@ -41,16 +45,10 @@
     <t>TO:E MAX SPORT PTE. LTD.</t>
   </si>
   <si>
-    <t>固定值</t>
-  </si>
-  <si>
     <t>INVOICE #:</t>
   </si>
   <si>
-    <t>2301-202511200002</t>
-  </si>
-  <si>
-    <t>PO record“EMAX-RO ”</t>
+    <t>ELEW20260525</t>
   </si>
   <si>
     <t>8 KAKI BUKIT AVENUE 4, #08-32,PREMIER @ KAKI BUKIT,</t>
@@ -59,9 +57,6 @@
     <t xml:space="preserve">DATE: </t>
   </si>
   <si>
-    <t>生成日期</t>
-  </si>
-  <si>
     <t xml:space="preserve"> SINGAPORE 415875</t>
   </si>
   <si>
@@ -80,9 +75,6 @@
     <t>To:KANSAS CITY, MO,USA</t>
   </si>
   <si>
-    <t>手动更新</t>
-  </si>
-  <si>
     <t xml:space="preserve"> PO#</t>
   </si>
   <si>
@@ -110,25 +102,196 @@
     <t>AMOUNT</t>
   </si>
   <si>
-    <t>括号内数值手动更新</t>
-  </si>
-  <si>
-    <t>FISHING REELS (1277PCS,$46,350.8)</t>
+    <t>FISHING REELS</t>
+  </si>
+  <si>
+    <t>CB2500.B2</t>
+  </si>
+  <si>
+    <t>21-44640</t>
+  </si>
+  <si>
+    <t>PCS</t>
+  </si>
+  <si>
+    <t>CB3000.B2</t>
+  </si>
+  <si>
+    <t>21-44641</t>
+  </si>
+  <si>
+    <t>CB4000.B2</t>
+  </si>
+  <si>
+    <t>21-44642</t>
+  </si>
+  <si>
+    <t>CB6000.B2</t>
+  </si>
+  <si>
+    <t>21-44644</t>
+  </si>
+  <si>
+    <t>CB8000.B2</t>
+  </si>
+  <si>
+    <t>21-44645</t>
+  </si>
+  <si>
+    <t>ORIGIN IN CHINA</t>
+  </si>
+  <si>
+    <t>PACKING LIST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C/T#:                    </t>
+  </si>
+  <si>
+    <t>Invoice No.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
+      <t>PO record AL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>列</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
+      <t>"INV#"</t>
+    </r>
+  </si>
+  <si>
+    <t>MADE IN CHINA</t>
+  </si>
+  <si>
+    <t>SAP PO#</t>
+  </si>
+  <si>
+    <t>Description of Goods</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Net Weight</t>
+  </si>
+  <si>
+    <t>Gross Weight</t>
+  </si>
+  <si>
+    <t>Measurement</t>
+  </si>
+  <si>
+    <t>CTNS</t>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
         <charset val="0"/>
       </rPr>
-      <t>RO new PO template A</t>
+      <t>客户</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
-        <color indexed="40"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> PO A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>列</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <charset val="0"/>
+      </rPr>
+      <t>"Purchasing Document"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t>PO record E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>列</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve">"description", </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PO record</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
@@ -137,207 +300,193 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF00B0F0"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"SAP NO."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <charset val="0"/>
       </rPr>
-      <t>"Purchasing Document"</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t>RO new PO template J</t>
+      <t>PO record AM</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
-        <color indexed="40"/>
+        <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
+        <charset val="0"/>
       </rPr>
       <t>列</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF00B0F0"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <charset val="0"/>
       </rPr>
-      <t>"Model",</t>
+      <t>"SHIP QTY"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve">PO record AE </t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
-        <color indexed="10"/>
-        <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
         <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve"> ZEBCO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color indexed="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>和</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color indexed="10"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t>LEW'S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color indexed="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>是否取同一列</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t>RO new PO template I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color indexed="40"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>列</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF00B0F0"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <charset val="0"/>
       </rPr>
-      <t>"Material"</t>
+      <t>"N/W"</t>
     </r>
+  </si>
+  <si>
+    <t>固定值</t>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF00B0F0"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <charset val="0"/>
       </rPr>
-      <t>data base M,N,O</t>
+      <t>PO record AF</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
-        <color indexed="40"/>
+        <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
+        <charset val="0"/>
       </rPr>
       <t>列</t>
     </r>
-  </si>
-  <si>
-    <t>PO record</t>
-  </si>
-  <si>
-    <t>CB2500.B2</t>
-  </si>
-  <si>
-    <t>21-44640</t>
-  </si>
-  <si>
-    <t>PCS</t>
-  </si>
-  <si>
-    <t>CB3000.B2</t>
-  </si>
-  <si>
-    <t>21-44641</t>
-  </si>
-  <si>
-    <t>CB4000.B2</t>
-  </si>
-  <si>
-    <t>21-44642</t>
-  </si>
-  <si>
-    <t>CB6000.B2</t>
-  </si>
-  <si>
-    <t>21-44644</t>
-  </si>
-  <si>
-    <t>CB8000.B2</t>
-  </si>
-  <si>
-    <t>21-44645</t>
-  </si>
-  <si>
-    <t>ORIGIN IN CHINA</t>
-  </si>
-  <si>
-    <t>PACKED IN 88 CTNS</t>
-  </si>
-  <si>
     <r>
-      <t>箱数取自</t>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <charset val="0"/>
+      </rPr>
+      <t>"G/W"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <charset val="0"/>
+      </rPr>
+      <t>PO record AJ</t>
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Times New Roman"/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
         <charset val="0"/>
       </rPr>
-      <t>PL</t>
+      <t>列</t>
     </r>
-  </si>
-  <si>
-    <t>THERE IS NO SOLID WOOD PACKING MATERIAL IN THIS SHIPMENT.</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <charset val="0"/>
+      </rPr>
+      <t>"total CBM"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <charset val="0"/>
+      </rPr>
+      <t>PO record AD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>列</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <charset val="0"/>
+      </rPr>
+      <t>"CTN"</t>
+    </r>
+  </si>
+  <si>
+    <t>KGS</t>
+  </si>
+  <si>
+    <t>CBM</t>
+  </si>
+  <si>
+    <t>TOTAL:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="13">
+  <numFmts count="15">
     <numFmt numFmtId="25" formatCode="\$#,##0.00_);\(\$#,##0.00\)"/>
     <numFmt numFmtId="26" formatCode="\$#,##0.00_);[Red]\(\$#,##0.00\)"/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="mmm/dd/yyyy"/>
-    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="178" formatCode="[$-409]d/mmm/yy;@"/>
-    <numFmt numFmtId="179" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="180" formatCode="0.00_ "/>
-    <numFmt numFmtId="181" formatCode="0_);\(0\)"/>
-    <numFmt numFmtId="182" formatCode="\$#,##0.00;\-\$#,##0.00"/>
+    <numFmt numFmtId="176" formatCode="0.0_);[Red]\(0.0\)"/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="178" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="179" formatCode="0_);\(0\)"/>
+    <numFmt numFmtId="180" formatCode="[$-409]d/mmm/yy;@"/>
+    <numFmt numFmtId="181" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="182" formatCode="0.00_ "/>
+    <numFmt numFmtId="183" formatCode="mmm/dd/yyyy"/>
+    <numFmt numFmtId="184" formatCode="\$#,##0.00;\-\$#,##0.00"/>
   </numFmts>
-  <fonts count="64">
+  <fonts count="73">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -349,8 +498,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="13"/>
-      <name val="Times New Roman"/>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -367,7 +517,7 @@
     </font>
     <font>
       <b/>
-      <sz val="28"/>
+      <sz val="24"/>
       <name val="Arial Black"/>
       <charset val="134"/>
     </font>
@@ -404,22 +554,89 @@
       <charset val="0"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF00B0F0"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <u/>
+      <b/>
       <sz val="12"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <name val="Arial Black"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -428,15 +645,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="9"/>
       <color rgb="FF00B0F0"/>
-      <name val="宋体"/>
+      <name val="Arial"/>
       <charset val="0"/>
     </font>
     <font>
@@ -731,27 +942,21 @@
     </font>
     <font>
       <sz val="9"/>
-      <color indexed="40"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF00B0F0"/>
-      <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="10"/>
-      <name val="Arial"/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
       <charset val="0"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="50">
@@ -769,6 +974,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -913,12 +1124,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1050,7 +1255,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1063,6 +1268,15 @@
       <right/>
       <top/>
       <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -1273,327 +1487,514 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="117">
+  <cellStyleXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="36" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="48" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="36" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="48" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="49" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="48" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="39" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="59" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="48" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="49" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="48" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="39" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="69" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="117" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="118" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="117" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="119" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="19" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="20" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="21" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="182" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1603,7 +2004,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1">
@@ -1612,35 +2013,17 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="55" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="183" fontId="1" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1655,111 +2038,87 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="26" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="26" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="26" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="26" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="26" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="182" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="26" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="26" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="26" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="26" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="27" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="26" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="25" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="26" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="1" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="26" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="117">
+  <cellStyles count="120">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
@@ -1877,6 +2236,9 @@
     <cellStyle name="說明文字" xfId="114"/>
     <cellStyle name="样式 1 2" xfId="115"/>
     <cellStyle name="中等" xfId="116"/>
+    <cellStyle name="25*62*210_PACKING LIST-V3" xfId="117"/>
+    <cellStyle name="常规_PACKING LIST-V3" xfId="118"/>
+    <cellStyle name="常规 5 2 2" xfId="119"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1917,8 +2279,163 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7378065" y="71755"/>
-          <a:ext cx="3866515" cy="927100"/>
+          <a:off x="6894195" y="71755"/>
+          <a:ext cx="4144010" cy="927100"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>153035</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>71755</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>460375</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>95885</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="圆角矩形 1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5825490" y="71755"/>
+          <a:ext cx="2924810" cy="925830"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -2339,599 +2856,527 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.5"/>
+  <dimension ref="A1:J29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.6"/>
   <cols>
-    <col min="1" max="1" width="17.75" style="5" customWidth="1"/>
-    <col min="2" max="2" width="13.375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="10.875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="13.25" style="5" customWidth="1"/>
-    <col min="5" max="5" width="40" style="5" customWidth="1"/>
-    <col min="6" max="6" width="13.125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="12.5" style="5" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="5" customWidth="1"/>
-    <col min="9" max="9" width="13.5" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="17.75" style="76" customWidth="1"/>
+    <col min="2" max="2" width="13.375" style="76" customWidth="1"/>
+    <col min="3" max="3" width="10.875" style="76" customWidth="1"/>
+    <col min="4" max="4" width="13.25" style="76" customWidth="1"/>
+    <col min="5" max="5" width="40" style="76" customWidth="1"/>
+    <col min="6" max="6" width="13.125" style="76" customWidth="1"/>
+    <col min="7" max="7" width="12.5" style="76" customWidth="1"/>
+    <col min="8" max="8" width="20.8303571428571" style="76" customWidth="1"/>
+    <col min="9" max="9" width="13.5" style="76" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="76"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="41.1" customHeight="1" spans="1:10">
-      <c r="A1" s="6" t="s">
+    <row r="1" s="72" customFormat="1" ht="41.1" customHeight="1" spans="1:10">
+      <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="8" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="15" customHeight="1" spans="1:10">
-      <c r="A2" s="9" t="s">
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+    </row>
+    <row r="2" s="72" customFormat="1" ht="15" customHeight="1" spans="1:10">
+      <c r="A2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="15" customHeight="1" spans="1:10">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="15" customHeight="1" spans="1:10">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A5" s="15"/>
-      <c r="B5" s="16"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-    </row>
-    <row r="6" s="2" customFormat="1" ht="27" customHeight="1" spans="1:10">
-      <c r="A6" s="20" t="s">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+    </row>
+    <row r="3" s="72" customFormat="1" ht="15" customHeight="1" spans="1:10">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+    </row>
+    <row r="4" s="72" customFormat="1" ht="15" customHeight="1" spans="1:10">
+      <c r="A4" s="79"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+    </row>
+    <row r="5" s="72" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
+      <c r="A5" s="80"/>
+      <c r="B5" s="81"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+    </row>
+    <row r="6" s="73" customFormat="1" ht="27" customHeight="1" spans="1:10">
+      <c r="A6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="21" t="s">
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="22"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="24" t="s">
+      <c r="H6" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="I6" s="90"/>
+      <c r="J6" s="66"/>
+    </row>
+    <row r="7" s="73" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A7" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="25" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="26"/>
-    </row>
-    <row r="7" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A7" s="20" t="s">
+      <c r="H7" s="91">
+        <v>46038</v>
+      </c>
+      <c r="I7" s="92"/>
+      <c r="J7" s="66"/>
+    </row>
+    <row r="8" s="73" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A8" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="E7" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="24" t="s">
+      <c r="B8" s="61"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="86"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="27">
-        <v>46038</v>
-      </c>
-      <c r="I7" s="21" t="s">
+      <c r="H8" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="26"/>
-    </row>
-    <row r="8" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A8" s="20" t="s">
+      <c r="I8" s="28"/>
+      <c r="J8" s="93"/>
+    </row>
+    <row r="9" s="73" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="95"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="66"/>
+    </row>
+    <row r="10" s="73" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A10" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="24" t="s">
+      <c r="B10" s="96"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="94"/>
+      <c r="G10" s="94"/>
+      <c r="H10" s="95"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="66"/>
+    </row>
+    <row r="11" s="73" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A11" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="22" t="s">
+      <c r="B11" s="96"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="87"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="94"/>
+      <c r="J11" s="97"/>
+    </row>
+    <row r="12" s="73" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A12" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="28"/>
-      <c r="J8" s="29" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A9" s="30"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A10" s="34" t="s">
+      <c r="B12" s="96"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="98"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="99"/>
+      <c r="J12" s="66"/>
+    </row>
+    <row r="13" s="74" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A13" s="61"/>
+      <c r="B13" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="34"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="26"/>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A11" s="34" t="s">
+      <c r="C13" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="34"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="22"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="35"/>
-    </row>
-    <row r="12" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A12" s="34" t="s">
+      <c r="D13" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="36" t="s">
+      <c r="E13" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="22"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="26"/>
-    </row>
-    <row r="13" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A13" s="20"/>
-      <c r="B13" s="31" t="s">
+      <c r="F13" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="G13" s="61"/>
+      <c r="H13" s="101" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="I13" s="99"/>
+      <c r="J13" s="66"/>
+    </row>
+    <row r="14" s="74" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A14" s="37"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="38" t="s">
+      <c r="D14" s="37"/>
+      <c r="E14" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="F14" s="103"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="104" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="20"/>
-      <c r="H13" s="39" t="s">
+      <c r="I14" s="99"/>
+      <c r="J14" s="66"/>
+    </row>
+    <row r="15" s="74" customFormat="1" ht="21.95" customHeight="1" spans="1:10">
+      <c r="A15" s="61"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="86"/>
+      <c r="F15" s="87"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="66"/>
+    </row>
+    <row r="16" s="74" customFormat="1" ht="21.95" customHeight="1" spans="1:10">
+      <c r="A16" s="61"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="37"/>
-      <c r="J13" s="26"/>
-    </row>
-    <row r="14" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A14" s="40"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40" t="s">
+      <c r="D16" s="62"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="107"/>
+      <c r="I16" s="99"/>
+      <c r="J16" s="66"/>
+    </row>
+    <row r="17" ht="15.95" customHeight="1" spans="1:10">
+      <c r="A17" s="61"/>
+      <c r="B17" s="42">
+        <v>4500028983</v>
+      </c>
+      <c r="C17" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="40"/>
-      <c r="E14" s="41" t="s">
+      <c r="D17" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="42"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="44" t="s">
+      <c r="E17" s="106">
+        <v>32.8</v>
+      </c>
+      <c r="F17" s="45">
+        <v>96</v>
+      </c>
+      <c r="G17" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="37"/>
-      <c r="J14" s="26"/>
-    </row>
-    <row r="15" s="3" customFormat="1" ht="21.95" customHeight="1" spans="1:10">
-      <c r="A15" s="20"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="45" t="s">
+      <c r="H17" s="107">
+        <f t="shared" ref="H17:H23" si="0">E17*F17</f>
+        <v>3148.8</v>
+      </c>
+      <c r="I17" s="99"/>
+      <c r="J17" s="66"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:10">
+      <c r="A18" s="61"/>
+      <c r="B18" s="42">
+        <v>4500028983</v>
+      </c>
+      <c r="C18" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="31"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="26"/>
-    </row>
-    <row r="16" s="3" customFormat="1" ht="21.95" customHeight="1" spans="1:10">
-      <c r="A16" s="20"/>
-      <c r="B16" s="46"/>
-      <c r="C16" s="47" t="s">
+      <c r="D18" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="31"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="26"/>
-    </row>
-    <row r="17" s="3" customFormat="1" ht="21.95" customHeight="1" spans="1:10">
-      <c r="A17" s="20"/>
-      <c r="B17" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="50"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="26"/>
-    </row>
-    <row r="18" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A18" s="20"/>
-      <c r="B18" s="46">
-        <v>4500028983</v>
-      </c>
-      <c r="C18" s="51" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="48">
-        <v>32.8</v>
-      </c>
-      <c r="F18" s="49">
-        <v>96</v>
-      </c>
-      <c r="G18" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18" s="50">
-        <f t="shared" ref="H18:H24" si="0">E18*F18</f>
-        <v>3148.8</v>
-      </c>
-      <c r="I18" s="37"/>
-      <c r="J18" s="26"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:10">
-      <c r="A19" s="20"/>
-      <c r="B19" s="46">
-        <v>4500028983</v>
-      </c>
-      <c r="C19" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="48">
+      <c r="E18" s="106">
         <v>33.1</v>
       </c>
-      <c r="F19" s="49">
+      <c r="F18" s="45">
         <v>262</v>
       </c>
-      <c r="G19" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="H19" s="50">
+      <c r="G18" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="107">
         <f t="shared" si="0"/>
         <v>8672.2</v>
       </c>
-      <c r="I19" s="37"/>
-      <c r="J19" s="26"/>
-    </row>
-    <row r="20" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A20" s="20"/>
-      <c r="B20" s="46">
+      <c r="I18" s="99"/>
+      <c r="J18" s="66"/>
+    </row>
+    <row r="19" ht="15.95" customHeight="1" spans="1:10">
+      <c r="A19" s="61"/>
+      <c r="B19" s="42">
         <v>4500028983</v>
       </c>
-      <c r="C20" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="51" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" s="48">
+      <c r="C19" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="106">
         <v>34.4</v>
       </c>
-      <c r="F20" s="49">
+      <c r="F19" s="45">
         <v>292</v>
       </c>
-      <c r="G20" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="H20" s="50">
+      <c r="G19" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="107">
         <f t="shared" si="0"/>
         <v>10044.8</v>
       </c>
-      <c r="I20" s="37"/>
-      <c r="J20" s="26"/>
-    </row>
-    <row r="21" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A21" s="20"/>
-      <c r="B21" s="46">
+      <c r="I19" s="99"/>
+      <c r="J19" s="66"/>
+    </row>
+    <row r="20" ht="15.95" customHeight="1" spans="1:10">
+      <c r="A20" s="61"/>
+      <c r="B20" s="42">
         <v>4500028983</v>
       </c>
-      <c r="C21" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="E21" s="48">
+      <c r="C20" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="106">
         <v>37.9</v>
       </c>
-      <c r="F21" s="49">
+      <c r="F20" s="45">
         <v>132</v>
       </c>
-      <c r="G21" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="H21" s="50">
+      <c r="G20" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="107">
         <f t="shared" si="0"/>
         <v>5002.8</v>
       </c>
-      <c r="I21" s="37"/>
-      <c r="J21" s="26"/>
-    </row>
-    <row r="22" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A22" s="20"/>
-      <c r="B22" s="46">
+      <c r="I20" s="99"/>
+      <c r="J20" s="66"/>
+    </row>
+    <row r="21" ht="15.95" customHeight="1" spans="1:10">
+      <c r="A21" s="61"/>
+      <c r="B21" s="42">
         <v>4500028983</v>
       </c>
-      <c r="C22" s="51" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="51" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="48">
+      <c r="C21" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="106">
         <v>40.4</v>
       </c>
-      <c r="F22" s="49">
+      <c r="F21" s="45">
         <f>252+173</f>
         <v>425</v>
       </c>
-      <c r="G22" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="H22" s="50">
+      <c r="G21" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="107">
         <f t="shared" si="0"/>
         <v>17170</v>
       </c>
-      <c r="I22" s="37"/>
-      <c r="J22" s="26"/>
-    </row>
-    <row r="23" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A23" s="20"/>
-      <c r="B23" s="46">
+      <c r="I21" s="99"/>
+      <c r="J21" s="66"/>
+    </row>
+    <row r="22" ht="15.95" customHeight="1" spans="1:10">
+      <c r="A22" s="61"/>
+      <c r="B22" s="42">
         <v>4500030322</v>
       </c>
-      <c r="C23" s="51" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="48">
+      <c r="C22" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="106">
         <v>32.8</v>
       </c>
-      <c r="F23" s="49">
+      <c r="F22" s="45">
         <v>16</v>
       </c>
-      <c r="G23" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="H23" s="50">
+      <c r="G22" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="107">
         <f t="shared" si="0"/>
         <v>524.8</v>
       </c>
-      <c r="I23" s="37"/>
-      <c r="J23" s="26"/>
-    </row>
-    <row r="24" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A24" s="20"/>
-      <c r="B24" s="46">
+      <c r="I22" s="99"/>
+      <c r="J22" s="66"/>
+    </row>
+    <row r="23" ht="15.95" customHeight="1" spans="1:10">
+      <c r="A23" s="61"/>
+      <c r="B23" s="42">
         <v>4500030322</v>
       </c>
-      <c r="C24" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="48">
+      <c r="C23" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="106">
         <v>33.1</v>
       </c>
-      <c r="F24" s="49">
+      <c r="F23" s="45">
         <v>54</v>
       </c>
-      <c r="G24" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="H24" s="50">
+      <c r="G23" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="107">
         <f t="shared" si="0"/>
         <v>1787.4</v>
       </c>
-      <c r="I24" s="37"/>
-      <c r="J24" s="26"/>
-    </row>
-    <row r="25" ht="15.5" spans="1:10">
-      <c r="A25" s="20"/>
-      <c r="B25" s="46"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="52"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="26"/>
-    </row>
-    <row r="26" ht="15.5" spans="1:10">
-      <c r="A26" s="43"/>
-      <c r="B26" s="43"/>
-      <c r="C26" s="43"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="26"/>
-    </row>
-    <row r="27" ht="15.5" spans="1:10">
-      <c r="A27" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="30"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="54">
-        <f>SUM(F16:F26)</f>
+      <c r="I23" s="99"/>
+      <c r="J23" s="66"/>
+    </row>
+    <row r="24" ht="17.6" spans="1:10">
+      <c r="A24" s="61"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="106"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="107"/>
+      <c r="I24" s="99"/>
+      <c r="J24" s="66"/>
+    </row>
+    <row r="25" ht="17.6" spans="1:10">
+      <c r="A25" s="35"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="104"/>
+      <c r="I25" s="99"/>
+      <c r="J25" s="66"/>
+    </row>
+    <row r="26" ht="17.6" spans="1:10">
+      <c r="A26" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="18"/>
+      <c r="C26" s="61"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="109">
+        <f>SUM(F16:F25)</f>
         <v>1277</v>
       </c>
-      <c r="G27" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="H27" s="55">
-        <f>SUM(H16:H26)</f>
+      <c r="G26" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="110">
+        <f>SUM(H16:H25)</f>
         <v>46350.8</v>
       </c>
-      <c r="I27" s="37"/>
-      <c r="J27" s="26"/>
-    </row>
-    <row r="28" s="4" customFormat="1" ht="21" customHeight="1" spans="1:10">
-      <c r="A28" s="30"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="26"/>
-    </row>
-    <row r="29" s="4" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A29" s="57" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="57"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="26"/>
-    </row>
-    <row r="30" s="4" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A30" s="57" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" s="57"/>
-      <c r="C30" s="58" t="s">
-        <v>47</v>
-      </c>
-      <c r="D30" s="38"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="26"/>
-    </row>
-    <row r="31" ht="15.5" spans="1:10">
-      <c r="A31" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="35"/>
-    </row>
-    <row r="32" ht="15.5" spans="1:10">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="35"/>
+      <c r="I26" s="99"/>
+      <c r="J26" s="66"/>
+    </row>
+    <row r="27" s="75" customFormat="1" ht="21" customHeight="1" spans="1:10">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="100"/>
+      <c r="E27" s="86"/>
+      <c r="F27" s="87"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="111"/>
+      <c r="I27" s="99"/>
+      <c r="J27" s="66"/>
+    </row>
+    <row r="28" s="75" customFormat="1" ht="19.2" spans="1:10">
+      <c r="A28" s="112" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="112"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="100"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="87"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="94"/>
+      <c r="I28" s="95"/>
+      <c r="J28" s="66"/>
+    </row>
+    <row r="29" ht="17.6" spans="1:10">
+      <c r="A29" s="61"/>
+      <c r="B29" s="61"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="86"/>
+      <c r="F29" s="87"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="94"/>
+      <c r="I29" s="94"/>
+      <c r="J29" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2947,4 +3392,632 @@
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O26"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6"/>
+  <cols>
+    <col min="1" max="1" width="4.4375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="14.5" style="5" customWidth="1"/>
+    <col min="3" max="3" width="10.8482142857143" style="5" customWidth="1"/>
+    <col min="4" max="4" width="8.70535714285714" style="5" customWidth="1"/>
+    <col min="5" max="5" width="23.375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="8.5625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="9.33035714285714" style="5" customWidth="1"/>
+    <col min="8" max="8" width="8.25" style="5" customWidth="1"/>
+    <col min="9" max="9" width="7.64285714285714" style="5" customWidth="1"/>
+    <col min="10" max="10" width="6.72321428571429" style="6" customWidth="1"/>
+    <col min="11" max="11" width="9" style="6" customWidth="1"/>
+    <col min="12" max="12" width="5.1875" style="6" customWidth="1"/>
+    <col min="13" max="13" width="7.64285714285714" style="7" customWidth="1"/>
+    <col min="14" max="16384" width="11" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="41" customHeight="1" spans="1:14">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="9"/>
+      <c r="H1" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="15" customHeight="1" spans="1:14">
+      <c r="A2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="13"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="15" customHeight="1" spans="1:14">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="14"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="15" customHeight="1" spans="1:14">
+      <c r="A4" s="15"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="17"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="16" customHeight="1" spans="1:14">
+      <c r="A5" s="18"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="21"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" ht="16" customHeight="1" spans="1:14">
+      <c r="A6" s="18"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="21"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="28"/>
+    </row>
+    <row r="7" s="2" customFormat="1" ht="16" customHeight="1" spans="1:14">
+      <c r="A7" s="18"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="28"/>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="16" customHeight="1" spans="1:14">
+      <c r="A8" s="35"/>
+      <c r="B8" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="37"/>
+      <c r="G8" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="38"/>
+      <c r="I8" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" s="39"/>
+      <c r="K8" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="L8" s="39"/>
+      <c r="M8" s="28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" ht="16" customHeight="1" spans="1:14">
+      <c r="A9" s="28"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="28"/>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="16" customHeight="1" spans="1:14">
+      <c r="A10" s="28"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="44"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="47"/>
+      <c r="L10" s="45"/>
+      <c r="M10" s="28"/>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="41" customHeight="1" spans="1:14">
+      <c r="A11" s="28"/>
+      <c r="B11" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="45"/>
+      <c r="G11" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="J11" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="L11" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="M11" s="51" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" ht="16" customHeight="1" spans="1:14">
+      <c r="A12" s="28"/>
+      <c r="B12" s="42">
+        <v>4500028983</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="53">
+        <v>96</v>
+      </c>
+      <c r="F12" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="46">
+        <f>38.59+3</f>
+        <v>41.59</v>
+      </c>
+      <c r="H12" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" s="47">
+        <f>45.4+3.3</f>
+        <v>48.7</v>
+      </c>
+      <c r="J12" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="K12" s="47">
+        <v>0.31</v>
+      </c>
+      <c r="L12" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="53">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" s="3" customFormat="1" ht="16" customHeight="1" spans="1:14">
+      <c r="A13" s="28"/>
+      <c r="B13" s="42">
+        <v>4500028983</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="53">
+        <v>262</v>
+      </c>
+      <c r="F13" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="46">
+        <v>117.67</v>
+      </c>
+      <c r="H13" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="I13" s="46">
+        <v>138.43</v>
+      </c>
+      <c r="J13" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="K13" s="47">
+        <v>0.78</v>
+      </c>
+      <c r="L13" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="M13" s="53">
+        <v>15</v>
+      </c>
+      <c r="N13" s="2"/>
+    </row>
+    <row r="14" s="3" customFormat="1" ht="16" customHeight="1" spans="1:14">
+      <c r="A14" s="28"/>
+      <c r="B14" s="42">
+        <v>4500028983</v>
+      </c>
+      <c r="C14" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="53">
+        <v>292</v>
+      </c>
+      <c r="F14" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="46">
+        <f>136.41+2.01</f>
+        <v>138.42</v>
+      </c>
+      <c r="H14" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" s="46">
+        <f>160.48+2.6</f>
+        <v>163.08</v>
+      </c>
+      <c r="J14" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="K14" s="47">
+        <v>0.83</v>
+      </c>
+      <c r="L14" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="M14" s="53">
+        <v>16</v>
+      </c>
+      <c r="N14" s="2"/>
+    </row>
+    <row r="15" s="3" customFormat="1" ht="16" customHeight="1" spans="1:14">
+      <c r="A15" s="28"/>
+      <c r="B15" s="42">
+        <v>4500028983</v>
+      </c>
+      <c r="C15" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="53">
+        <v>132</v>
+      </c>
+      <c r="F15" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="46">
+        <v>101.35</v>
+      </c>
+      <c r="H15" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="I15" s="46">
+        <v>119.24</v>
+      </c>
+      <c r="J15" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="K15" s="47">
+        <v>0.58</v>
+      </c>
+      <c r="L15" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="M15" s="53">
+        <v>11</v>
+      </c>
+      <c r="N15" s="2"/>
+    </row>
+    <row r="16" s="3" customFormat="1" ht="16" customHeight="1" spans="1:14">
+      <c r="A16" s="28"/>
+      <c r="B16" s="42">
+        <v>4500028983</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="53">
+        <v>425</v>
+      </c>
+      <c r="F16" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="46">
+        <f>245.62+175.44</f>
+        <v>421.06</v>
+      </c>
+      <c r="H16" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="I16" s="47">
+        <f>288.96+206.4</f>
+        <v>495.36</v>
+      </c>
+      <c r="J16" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="K16" s="47">
+        <f>1.55+1.11</f>
+        <v>2.66</v>
+      </c>
+      <c r="L16" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="M16" s="53">
+        <v>36</v>
+      </c>
+      <c r="N16" s="2"/>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="16" customHeight="1" spans="1:15">
+      <c r="A17" s="28"/>
+      <c r="B17" s="42">
+        <v>4500030322</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="53">
+        <v>16</v>
+      </c>
+      <c r="F17" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="46">
+        <v>6.77</v>
+      </c>
+      <c r="H17" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="I17" s="46">
+        <v>7.96</v>
+      </c>
+      <c r="J17" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="K17" s="47">
+        <v>0.05</v>
+      </c>
+      <c r="L17" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" ht="16" customHeight="1" spans="1:15">
+      <c r="A18" s="28"/>
+      <c r="B18" s="42">
+        <v>4500030322</v>
+      </c>
+      <c r="C18" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="53">
+        <v>54</v>
+      </c>
+      <c r="F18" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="46">
+        <v>24.17</v>
+      </c>
+      <c r="H18" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="I18" s="46">
+        <v>28.44</v>
+      </c>
+      <c r="J18" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="K18" s="47">
+        <v>0.16</v>
+      </c>
+      <c r="L18" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="M18" s="53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" s="4" customFormat="1" ht="16" customHeight="1" spans="1:15">
+      <c r="A19" s="54"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="60"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="28"/>
+    </row>
+    <row r="20" ht="16" customHeight="1" spans="1:15">
+      <c r="A20" s="61" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="32"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="41">
+        <f>SUM(E10:E19)</f>
+        <v>1277</v>
+      </c>
+      <c r="F20" s="62" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="47">
+        <f>SUM(G10:G19)</f>
+        <v>851.03</v>
+      </c>
+      <c r="H20" s="63" t="s">
+        <v>57</v>
+      </c>
+      <c r="I20" s="63">
+        <f>SUM(I10:I19)</f>
+        <v>1001.21</v>
+      </c>
+      <c r="J20" s="63" t="s">
+        <v>57</v>
+      </c>
+      <c r="K20" s="63">
+        <f>SUM(K10:K19)</f>
+        <v>5.37</v>
+      </c>
+      <c r="L20" s="62" t="s">
+        <v>58</v>
+      </c>
+      <c r="M20" s="63">
+        <f>SUM(M10:M19)</f>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="16" customHeight="1" spans="1:15">
+      <c r="A21" s="64"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="66"/>
+      <c r="J21" s="64"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="64"/>
+      <c r="M21" s="66"/>
+      <c r="O21" s="71"/>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="16" customHeight="1" spans="1:15">
+      <c r="A22" s="64"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="64"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="64"/>
+      <c r="M22" s="66"/>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="I25" s="6"/>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="I26" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="H1:M4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0" right="0" top="0.196527777777778" bottom="0.196527777777778" header="0.511111111111111" footer="0.511111111111111"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>